--- a/audit-work-programs/IESP-DCRA-WorkProgram.xlsx
+++ b/audit-work-programs/IESP-DCRA-WorkProgram.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,11 @@
       <color rgb="002F5496"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -103,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,16 +117,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -925,148 +935,492 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LIMITATIONS</t>
+          <t>SAMPLING METHODOLOGY</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>1. Limited assurance engagement — conclusions based on procedures performed, not absolute assurance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>2. Point-in-time (design adequacy) or period assessment (operating effectiveness).</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sampling Approach:</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Judgmental (not statistical) — appropriate for limited assurance engagements under BNM RMiT. Sample sizes are based on population size and control risk tier.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>3. Reliance on management representations and documentation provided.</t>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Sample Size Table:</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>4. Scope guided by BNM RMiT (BNM/RH/PD 028-98, 28 Nov 2025).</t>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Population Size</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Standard Risk</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Rationale</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>5. Does not constitute legal or regulatory advice.</t>
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Full coverage feasible</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>6. The IESP remains solely responsible for the sufficiency of work performed.</t>
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>6-15</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>~25-40% coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>16-50</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Sufficient for pattern detection</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>SIGN-OFF</t>
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Diminishing returns beyond this</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Lead Assessor:</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>________________________</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>Date:</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>______________</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Quality Reviewer:</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>________________________</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>Date:</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>______________</t>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Cap with stratification</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
+          <t>Time-Based Evidence Coverage:</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Evidence Type</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Coverage Period</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Board/committee reports</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Last 4 quarters</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Full annual governance cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Operational records (incidents, changes, patches)</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Last 3-6 months</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Recent operating effectiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Annual processes (risk assessment, DR test, pen test)</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Last 12 months</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Full cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Continuous monitoring (SOC, logs, alerts)</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Last 30 days</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Current state verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Policies and frameworks</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Current version + prior</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Change tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Control Risk Tiers:</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Sampling Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Governance framework, SOC, incident response, regulatory notification, BCM, customer data protection</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>High risk samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Most controls (risk assessment, vuln mgmt, vendor assessment, change mgmt, etc.)</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Standard risk samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Emerging tech, specialised areas — may be N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Standard if applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>1. Limited assurance engagement — conclusions based on procedures performed, not absolute assurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2. Point-in-time (design adequacy) or period assessment (operating effectiveness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>3. Reliance on management representations and documentation provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>4. Scope guided by BNM RMiT (BNM/RH/PD 028-98, 28 Nov 2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>5. Does not constitute legal or regulatory advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>6. The IESP remains solely responsible for the sufficiency of work performed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SIGN-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Lead Assessor:</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>________________________</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>______________</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Quality Reviewer:</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>________________________</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>______________</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
           <t>Entity Representative:</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>________________________</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>______________</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
+    <mergeCell ref="A76:M76"/>
     <mergeCell ref="A14:M14"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A53:M53"/>
     <mergeCell ref="A29:M29"/>
     <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A52:M52"/>
+    <mergeCell ref="A81:M81"/>
     <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A77:M77"/>
+    <mergeCell ref="A83:M83"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A51:M51"/>
     <mergeCell ref="A36:M36"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B51:M51"/>
+    <mergeCell ref="A79:M79"/>
+    <mergeCell ref="A78:M78"/>
     <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="A80:M80"/>
+    <mergeCell ref="A75:M75"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="A50:M50"/>
-    <mergeCell ref="A56:M56"/>
     <mergeCell ref="A21:M21"/>
-    <mergeCell ref="A55:M55"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A42:M42"/>
   </mergeCells>
@@ -1149,96 +1503,96 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Platform / CSP</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Service Models (IaaS/PaaS/SaaS)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Regions</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Contract Ref</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
+      <c r="B14" s="9" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1248,156 +1602,156 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>System / Application Name</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Criticality</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Data Classification</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr"/>
-      <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr"/>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr"/>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="7" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr"/>
-      <c r="C20" s="7" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr"/>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr"/>
-      <c r="C22" s="7" t="inlineStr"/>
-      <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr"/>
-      <c r="F22" s="7" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr"/>
-      <c r="C23" s="7" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr"/>
-      <c r="C24" s="7" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr"/>
+      <c r="B24" s="9" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr"/>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr"/>
-      <c r="C25" s="7" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr"/>
+      <c r="B25" s="9" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr"/>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr"/>
-      <c r="C26" s="7" t="inlineStr"/>
-      <c r="D26" s="7" t="inlineStr"/>
-      <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr"/>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr"/>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1523,241 +1877,241 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Responsible</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>P-01</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Confirm engagement trigger and regulatory basis</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>P-02</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Issue engagement letter with scope, timeline, and deliverables</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>P-03</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Confirm IESP team qualifications and independence (Part C compliance)</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>P-04</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Issue Document Request List (DRL) to the FI</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>P-05</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Obtain and review prior assessment reports and remediation status</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>P-06</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Identify platforms/CSPs in scope and complete scoping sheet</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>P-07</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Identify critical systems/workloads in scope</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>P-08</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Define assessment period and sampling approach</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>P-09</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Determine engagement mode: design adequacy (pre-impl) or operating effectiveness (attestation)</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>P-10</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Determine if higher-risk services criteria apply (customer data, cross-border)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>P-11</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Schedule site visits / remote assessment sessions</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>P-12</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Conduct kick-off meeting with FI management</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>P-13</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Receive and catalogue DRL responses</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>P-14</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Finalise scoping memorandum</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1773,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1792,113 +2146,132 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Sub-Procedure</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Assessment Procedures</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Expected Evidence</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Procedures Performed</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Evidence Obtained</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Observation / Findings</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Recommendations</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Domain 1 — DC Resilience and Availability Objectives (10.24)</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="11" t="n"/>
-      <c r="M2" s="11" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>DC resilience objectives must align with business recovery requirements. Expect quantified targets (availability %, RTO, RPO) approved by committee. Misaligned objectives mean the DC cannot support business recovery.</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>DCRA-01</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Resilience Objectives</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Objectives alignment</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>1. Obtain DC resilience strategy.
 2. Extract resilience targets (availability %, RTO, RPO).
@@ -1906,109 +2279,128 @@
 4. Check targets approved by appropriate committee.</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>DC resilience strategy; Business recovery objectives matrix; Committee approval minutes</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>DCRA-02</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Resilience Objectives</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Periodic review</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>1. Check version history.
 2. Confirm annual review or upon material change.
 3. Verify business requirement changes triggered updates.</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Document version history; Change log; Review sign-off records</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Domain 2 — Redundancy and Single Points of Failure (10.25)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Critical infrastructure must have no single points of failure. Expect N+1 or 2N redundancy, diverse paths, tested failover. A single failure in power, cooling, or network can cause a DC outage.</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>DCRA-03</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Redundancy</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Redundant capacity</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>1. Obtain redundancy design (N+1, 2N, 2N+1).
 2. For each critical layer (power, cooling, network), confirm redundancy.
@@ -2016,45 +2408,45 @@
 4. Check redundant capacity handles full load on failover.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Redundancy design specs; Capacity planning reports; Site inspection photographs</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>DCRA-04</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Redundancy</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Multiple distribution paths</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>1. Review electrical single-line diagrams for dual feeds.
 2. Review network diagrams for diverse carrier paths.
@@ -2062,45 +2454,45 @@
 4. Verify through site walk.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Electrical single-line diagrams; Network path diversity docs; Site walk observations</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>DCRA-05</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Redundancy</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>SPOF analysis</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>1. Obtain SPOF analysis per DC.
 2. Walk through each SPOF and confirm mitigations.
@@ -2108,45 +2500,45 @@
 4. Check SPOF analysis periodically refreshed.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>SPOF analysis/register; Mitigation action plans; Site walk findings</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>DCRA-06</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Redundancy</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Failover testing</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>1. Obtain failover test plans and results (UPS, generators, cooling, switches).
 2. Review test frequency (at least annual).
@@ -2154,109 +2546,128 @@
 4. Check test failures remediated.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Failover test plans; Test result reports; Corrective action records</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Domain 3 — Physical Security and Environmental Controls (10.26)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Physical security protects against unauthorised access and environmental threats. Expect multi-layered access, environmental monitoring, fire suppression, hazard assessment. Physical compromise bypasses all logical controls.</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>DCRA-07</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Physical Security</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Dedicated space</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>1. Confirm DC in dedicated space.
 2. Verify physical separation from public areas.
 3. Check walls extend true floor to true ceiling.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Site inspection observations; Building layout plans; Lease/facility agreements</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>DCRA-08</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Physical Security</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Multi-layered access controls</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>1. Walk access path from perimeter to rack.
 2. Verify independent controls at each layer.
@@ -2265,45 +2676,45 @@
 5. Sample-check access list against HR for terminated staff.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Physical security policy; Access control config; Access list vs HR reconciliation; Site walk observations</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>DCRA-09</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Physical Security</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Disaster-prone location assessment</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>1. Obtain site risk assessment (flood, earthquake, lightning).
 2. Cross-reference against hazard maps.
@@ -2311,45 +2722,45 @@
 4. Check assessment periodically updated.</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Site risk assessment; Hazard map cross-reference; Mitigation evidence</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
-      <c r="M13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>DCRA-10</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Environmental Controls</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Electrical infrastructure</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>1. Review UPS configuration (N+1 or 2N).
 2. Verify UPS runtime (min 15 min).
@@ -2358,45 +2769,45 @@
 5. Verify fuel replenishment contracts.</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>UPS specs and test reports; Generator load test reports; ATS test records; Fuel supply contracts</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
-      <c r="M14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>DCRA-11</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Environmental Controls</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Thermal management</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>1. Review cooling design (N+1 min).
 2. Check cooling load vs capacity.
@@ -2405,45 +2816,45 @@
 5. Review hot/cold aisle containment.</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Cooling design docs; Capacity reports; Monitoring config; Alert thresholds</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>DCRA-12</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Environmental Controls</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Fire suppression and monitoring</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>1. Confirm VESDA or equivalent.
 2. Verify gas-based suppression with current inspections.
@@ -2452,45 +2863,45 @@
 5. Review environmental incident response procedures.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Fire suppression certificates; VESDA config; Water leak detection; Monitoring dashboard; Environmental IR procedures</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
-      <c r="M16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>DCRA-13</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Asset Management</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Hardware lifecycle</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>1. Obtain hardware asset register.
 2. Sample-check physical assets against register.
@@ -2498,64 +2909,83 @@
 4. Check secure data destruction for decommissioned equipment.</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Hardware asset register; Physical verification; EOL/EOS tracker; Data destruction certificates</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="8" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Domain 4 — DC Operations and Control Procedures (10.27)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="11" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Operational controls ensure stable, monitored DC operations. Expect automated monitoring, controlled changes, incident management with RCA. Uncontrolled operations lead to avoidable outages.</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>DCRA-14</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>DC Operations</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Automated monitoring</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>1. Obtain monitoring tool inventory (DCIM, BMS, network).
 2. Verify coverage of critical parameters.
@@ -2563,45 +2993,45 @@
 4. Confirm NOC/SOC integration.</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Tool inventory; Monitoring coverage matrix; Sample alerts; NOC/SOC integration</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>DCRA-15</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>DC Operations</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Batch processing controls</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>1. Obtain batch job procedures.
 2. Verify jobs have defined run windows, dependencies, error handling.
@@ -2609,45 +3039,45 @@
 4. Check schedule changes controlled.</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Batch scheduling procedures; Job scheduler config; Failure logs; Change approval records</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
-      <c r="M20" s="8" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>DCRA-16</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>DC Operations</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>Change management</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>1. Obtain DC change management procedure.
 2. Sample 10 infrastructure changes.
@@ -2655,45 +3085,45 @@
 4. Check emergency changes follow defined process.</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>Change management procedure; 10 sampled change records; Emergency change records</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>DCRA-17</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>DC Operations</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Error and incident handling</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>1. Obtain DC incident management procedure.
 2. Review incident log (6 months).
@@ -2701,64 +3131,83 @@
 4. Check RCA findings led to preventive actions.</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Incident management procedure; Incident log (6 months); RCA reports; Preventive action tracker</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr"/>
-      <c r="J22" s="8" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
-      <c r="M22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Domain 5 — Segregation of Incompatible Activities (10.28)</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Segregation prevents unauthorised changes and maintains environment integrity. Expect production isolation, controlled vendor access, SoD enforcement. Without segregation, a single actor can compromise production.</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>DCRA-18</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Segregation</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Vendor access controls</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>1. Review vendor/third-party access policy.
 2. Check pre-approved access requests.
@@ -2767,45 +3216,45 @@
 5. Confirm access revoked promptly.</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Vendor access policy; Access request forms; Escort logs; Access log reconciliation</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr"/>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>DCRA-19</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PLATFORM</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Segregation</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Production segregation</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>1. Review logical and physical segregation (prod vs non-prod).
 2. Verify developers have no direct production access.
@@ -2813,45 +3262,45 @@
 4. Confirm non-prod data masked.</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>Environment segregation architecture; Access control matrices; Network segmentation; Data masking procedures</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="8" t="inlineStr"/>
-      <c r="M25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>DCRA-20</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Segregation</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Segregation of duties</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>1. Obtain DC operations RACI.
 2. Verify incompatible duties separated.
@@ -2859,30 +3308,35 @@
 4. Review privileged access usage logs (3 months).</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>RACI matrix; Role definitions; Privileged access list; Privileged access usage logs</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="8" t="inlineStr"/>
-      <c r="J26" s="8" t="inlineStr"/>
-      <c r="K26" s="8" t="inlineStr"/>
-      <c r="L26" s="8" t="inlineStr"/>
-      <c r="M26" s="8" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A18:M18"/>
+  <mergeCells count="10">
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A7:M7"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A28:M28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2894,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2913,113 +3367,132 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Sub-Procedure</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Assessment Procedures</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Expected Evidence</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Procedures Performed</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Evidence Obtained</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Observation / Findings</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Recommendations</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Item 1(a) — Access Control</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="11" t="n"/>
-      <c r="M2" s="11" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Access control is foundational — who can access what. Expect policy-driven provisioning, periodic reviews, PAM controls, timely revocation. Excessive access is the most common audit finding.</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>PD-01</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Access Control</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Access control policies and mechanisms</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>1. Obtain the FI's access control policy and supporting standards.
 2. Verify policy covers user registration, de-registration, access provisioning, and privilege management.
@@ -3028,45 +3501,45 @@
 5. Verify access revocation upon termination — sample 10 recent leavers/transfers.</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Access control policy; User access provisioning records; Access review reports; HR leaver/transfer list vs. access revocation logs</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>PD-02</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Access Control</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Privileged access management</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>1. Obtain the PAM policy or standard.
 2. Obtain the list of all privileged accounts (system admin, DBA, root, domain admin).
@@ -3075,64 +3548,83 @@
 5. Review privileged session logs for the past 3 months for anomalies.</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>PAM policy; Privileged account inventory; PAM tool configuration and logs; Session recording samples</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Item 1(b) — Physical and Environmental Security</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Physical controls protect technology assets from unauthorised access and environmental threats. Expect multi-layered access, CCTV, environmental monitoring. Physical compromise bypasses logical controls.</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>PD-03</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Physical Security</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Physical security controls</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>1. Identify all sensitive areas (data centres, server rooms, network rooms).
 2. Verify multi-layered physical access controls (badge, biometric, PIN).
@@ -3141,45 +3633,45 @@
 5. Sample-check physical access logs against approved access lists.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Physical security policy; Access control system config; Visitor logs; CCTV coverage map; Physical access log reconciliation</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>PD-04</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Physical Security</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Environmental controls</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>1. Verify fire detection and suppression systems are current on inspections.
 2. Check water leak detection.
@@ -3187,64 +3679,83 @@
 4. Confirm environmental incident response procedures are tested.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Fire system inspection certificates; Water leak detection layout; Environmental monitoring dashboards; Incident response test records</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>Inspection / Observation</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Item 1(c) — Operations Security</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Operational controls ensure systems are managed securely. Expect documented procedures, controlled changes, tested backups, malware protection, vulnerability management. Operational failures cause avoidable incidents.</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>PD-05</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Operations Security</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Operational procedures and controls</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>1. Obtain documented operating procedures (change mgmt, capacity mgmt, backup, malware protection).
 2. Verify change management — sample 10 changes with full lifecycle.
@@ -3252,45 +3763,45 @@
 4. Verify anti-malware deployed with current signatures.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Operating procedures; 10 sampled change records; Backup schedule and restore test results; Anti-malware deployment reports</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>PD-06</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Operations Security</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Vulnerability management and patching</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>1. Obtain vulnerability management policy and patching SLAs.
 2. Review most recent vulnerability scan results.
@@ -3298,64 +3809,83 @@
 4. Verify exceptions are formally risk-accepted.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Vulnerability management policy; Scan reports; Patch compliance dashboard; Risk acceptance records</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Item 1(d) — Communications Security</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Network controls protect data in transit and network integrity. Expect segmentation, least-privilege firewall rules, encryption, IDS/IPS. Network compromise provides access to all connected systems.</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
+      <c r="J15" s="14" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>PD-07</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Communications Security</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Network security and secure communications</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>1. Review network segmentation.
 2. Verify firewall rules — sample 20 rules for least-privilege.
@@ -3364,64 +3894,83 @@
 5. Check IDS/IPS deployed at critical boundaries.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Network architecture diagram; Firewall rule base sample; TLS configuration; IDS/IPS deployment and alert records</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Item 1(e) — Incident Management</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Incident management ensures timely detection, response, and recovery. Expect 24/7 SOC, SIEM, IR playbooks, annual exercises. Without incident management, breaches escalate unchecked.</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>PD-08</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Incident Management</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Incident management framework</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>1. Obtain incident management policy and procedures.
 2. Verify incident classification scheme.
@@ -3430,45 +3979,45 @@
 5. Confirm regulatory notification procedures.</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Incident management policy; Classification matrix; Incident log (12 months); RCA reports; Regulatory notification records</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
-      <c r="M14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>PD-09</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Incident Management</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Detection and response capabilities</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>1. Confirm SOC operates 24/7.
 2. Verify SIEM deployment with critical log sources.
@@ -3477,64 +4026,83 @@
 5. Verify annual IR drills/tabletop exercises.</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>SOC operational documentation; SIEM log source inventory; 15 sampled alert records; IR playbooks; Drill/tabletop reports</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Inspection / Inquiry</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Item 1(f) — Business Continuity</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Business continuity ensures operations continue during disruptions. Expect BCP/DRP with cyber scenarios, tested DR including security controls, redundant security infrastructure. Untested DR fails when needed.</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>PD-10</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Business Continuity</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Security in BCP/DRP</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>1. Obtain BCP and IT DRP.
 2. Verify security requirements addressed in BCP/DRP.
@@ -3542,45 +4110,45 @@
 4. Verify recovery procedures include security validation.</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>BCP and IT DRP; Security requirements in BCP/DRP; Cyber incident scenarios; Recovery security validation checklists</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="8" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>PD-11</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Business Continuity</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>BCP/DRP testing with security controls</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>1. Review most recent BCP/DRP test.
 2. Verify security controls tested during DR exercise.
@@ -3588,45 +4156,45 @@
 4. Verify DR site maintains equivalent security posture.</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>BCP/DRP test plan and results; Security test components; DR site security assessment; Remediation tracker</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr"/>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
-      <c r="M18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>PD-12</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Business Continuity</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>Redundancy of security infrastructure</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>1. Identify critical security infrastructure and verify HA configuration.
 2. Confirm failover tested.
@@ -3634,64 +4202,83 @@
 4. Check licenses valid at DR site.</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>Security infrastructure HA architecture; Failover test records; DR monitoring evidence; License/subscription records</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Item 2(a) — Customer Identity Authentication</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="11" t="n"/>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Customer authentication protects online services from unauthorised access. Expect MFA, secure sessions, strong cryptography, anti-session-fixation. Weak authentication directly exposes customers.</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>PD-13</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Customer Authentication</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Session and MITM protection</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>1. Review session management controls.
 2. Verify TLS 1.2+, HSTS, certificate validity.
@@ -3700,45 +4287,45 @@
 5. Verify certificate pinning for mobile apps.</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>TLS scan results; Session management config; Application security assessment; Mobile cert pinning evidence</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>PD-14</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Customer Authentication</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Internal controls for online systems</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>1. Verify application hardening.
 2. Review app security testing results (SAST, DAST, pen test).
@@ -3746,45 +4333,45 @@
 4. Check segmentation from corporate network.</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Hardening standards; App security test reports; Database security config; Network segmentation evidence</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr"/>
-      <c r="J22" s="8" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
-      <c r="M22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>PD-15</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Customer Authentication</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Multi-level authentication</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>1. Review authentication architecture.
 2. Verify MFA for login and high-risk transactions.
@@ -3793,45 +4380,45 @@
 5. Assess authentication strength relative to transaction risk.</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>Authentication architecture; MFA config; OTP/out-of-band mechanism; Risk-based authentication rules</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="8" t="inlineStr"/>
-      <c r="J23" s="8" t="inlineStr"/>
-      <c r="K23" s="8" t="inlineStr"/>
-      <c r="L23" s="8" t="inlineStr"/>
-      <c r="M23" s="8" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>PD-16</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Customer Authentication</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Session handling and credential storage</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>1. Verify session timeouts (idle and absolute).
 2. Confirm concurrent session controls.
@@ -3840,45 +4427,45 @@
 5. Review account lockout configuration.</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>Session management config; Password hashing evidence; Auth database access controls; Account lockout config</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr"/>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>PD-17</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Customer Authentication</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Cryptographic implementation</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>1. Review cryptographic standards (AES-256, RSA-2048+, ECDSA P-256+).
 2. Verify key management practices.
@@ -3886,64 +4473,83 @@
 4. Verify crypto implementation reviewed/tested.</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>Cryptographic standards document; Key management procedures; HSM config; Crypto assessment results</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="8" t="inlineStr"/>
-      <c r="M25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Item 2(b) — Transaction Authentication</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="11" t="n"/>
-      <c r="J26" s="11" t="n"/>
-      <c r="K26" s="11" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="11" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Transaction authentication ensures non-repudiation and integrity. Expect transaction signing, tamper-evident audit trails, mutual authentication. Without non-repudiation, disputes cannot be resolved.</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>PD-18</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Transaction Authentication</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>Proof of origin and integrity</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>1. Review transaction signing/MAC mechanisms.
 2. Verify records include origin, timestamp, hash, integrity verification.
@@ -3951,45 +4557,45 @@
 4. Check logs sufficient for dispute resolution.</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Transaction authentication mechanism; Sample transaction records; Audit trail controls; Log retention policy</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="8" t="inlineStr"/>
-      <c r="J27" s="8" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr"/>
-      <c r="M27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>PD-19</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Transaction Authentication</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Secure delivery and mutual authentication</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>1. Verify delivery channel secured end-to-end.
 2. Check alerts for high-risk transaction types.
@@ -3997,64 +4603,83 @@
 4. Review triggers for additional authentication.</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Channel security architecture; Transaction alert config; Mutual authentication implementation; Authentication trigger criteria</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="8" t="inlineStr"/>
-      <c r="J28" s="8" t="inlineStr"/>
-      <c r="K28" s="8" t="inlineStr"/>
-      <c r="L28" s="8" t="inlineStr"/>
-      <c r="M28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Item 2(c) — Segregation of Duties</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>SoD prevents single-person control over critical operations. Expect maker-checker, privileged user reviews, tamper-resistant authorisation. SoD failures enable fraud.</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>PD-20</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Segregation of Duties</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Dual control for online transactions</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>1. Identify critical functions in online transaction systems.
 2. Verify maker-checker for critical operations.
@@ -4062,45 +4687,45 @@
 4. Verify unauthorised access detection.</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>Access control matrices; Maker-checker config; Dual control workflow; Unauthorised access detection controls</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr"/>
-      <c r="J30" s="8" t="inlineStr"/>
-      <c r="K30" s="8" t="inlineStr"/>
-      <c r="L30" s="8" t="inlineStr"/>
-      <c r="M30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>PD-21</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Segregation of Duties</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Authorisation database integrity</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>1. Verify authorisation database is tamper-resistant.
 2. Confirm changes require approval and are logged.
@@ -4108,64 +4733,83 @@
 4. Check reviews result in revocation of unnecessary access.</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>Auth database access controls; Change logs; Privileged user review records; Revocation evidence</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="8" t="inlineStr"/>
-      <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr"/>
-      <c r="L31" s="8" t="inlineStr"/>
-      <c r="M31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Item 2(d) — Data Integrity</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="11" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="12" t="n"/>
+      <c r="H41" s="12" t="n"/>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
+      <c r="K41" s="12" t="n"/>
+      <c r="L41" s="12" t="n"/>
+      <c r="M41" s="12" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>Data integrity controls prevent tampering and ensure confidentiality. Expect E2E encryption, defence-in-depth, pen testing, audit trails. Data integrity failure causes financial loss and regulatory breach.</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>PD-22</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Data Integrity</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>End-to-end encryption and multi-layer security</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>1. Verify E2E encryption for external communications.
 2. Review multi-layer network security (defence-in-depth).
@@ -4173,45 +4817,45 @@
 4. Verify security devices current on firmware/signatures.</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>Encryption architecture; Multi-layer security diagram; Security device inventory; Management and monitoring evidence</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr"/>
-      <c r="J33" s="8" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr"/>
-      <c r="L33" s="8" t="inlineStr"/>
-      <c r="M33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>PD-23</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Data Integrity</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>Absence of single points of failure</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>1. Review network architecture for SPOF.
 2. Verify redundancy at each critical layer.
@@ -4219,45 +4863,45 @@
 4. Check SPOF analysis documented.</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Network architecture with redundancy; SPOF analysis; Failover test results; SPOF review history</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr"/>
-      <c r="J34" s="8" t="inlineStr"/>
-      <c r="K34" s="8" t="inlineStr"/>
-      <c r="L34" s="8" t="inlineStr"/>
-      <c r="M34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr"/>
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>PD-24</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>ORG</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Data Integrity</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Security assessment and audit trails</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>1. Obtain most recent pen test and network security assessment.
 2. Verify testing by qualified party within 12 months.
@@ -4266,45 +4910,45 @@
 5. Confirm logs tamper-protected and retained.</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>Pen test report; Network security assessment; Audit trail config and sample logs; Log integrity controls</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr"/>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
-      <c r="L35" s="8" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>PD-25</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Data Integrity</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Data confidentiality and risk-based auth</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>1. Verify confidentiality controls (encryption, masking, access controls).
 2. Confirm data classification applied.
@@ -4312,64 +4956,83 @@
 4. Check customers receive timely transaction notifications.</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Data classification scheme; Encryption and masking config; Risk-based auth rules; Customer notification samples</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr"/>
-      <c r="M36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Item 2(e) — Mobile Device Risks</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="B47" s="12" t="n"/>
+      <c r="C47" s="12" t="n"/>
+      <c r="D47" s="12" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="n"/>
+      <c r="G47" s="12" t="n"/>
+      <c r="H47" s="12" t="n"/>
+      <c r="I47" s="12" t="n"/>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="12" t="n"/>
+      <c r="L47" s="12" t="n"/>
+      <c r="M47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>Mobile apps require additional protections due to the untrusted device environment. Expect jailbreak detection, secure storage, certificate pinning, fake app monitoring. Mobile-specific attacks bypass server-side controls.</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>PD-26</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Mobile Device Security</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Mobile app security baseline</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>1. Confirm minimum OS version enforced and jailbreak/root detection.
 2. Review most recent mobile pen test.
@@ -4377,45 +5040,45 @@
 4. Confirm secure E2E communication (cert pinning, TLS 1.2+).</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>OS version enforcement; Jailbreak/root detection; Mobile pen test report; Remediation evidence; Communication security config</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="8" t="inlineStr"/>
-      <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr"/>
-      <c r="M38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>PD-27</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Mobile Device Security</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Mobile data protection</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>1. Verify sensitive data not stored on device or only in secure enclaves.
 2. Confirm cache/logs sanitised.
@@ -4423,45 +5086,45 @@
 4. Check remote wipe capability.</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>Mobile app security architecture; Data storage review; Secure enclave usage; Remote wipe documentation</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr"/>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr"/>
-      <c r="L39" s="8" t="inlineStr"/>
-      <c r="M39" s="8" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr"/>
+      <c r="K50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>PD-28</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Mobile Device Security</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Transaction notification and codes</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>1. Verify transaction notifications (push, SMS, email).
 2. Verify suspicious transaction alerts.
@@ -4469,45 +5132,45 @@
 4. Verify code expiry (2-5 min) and single-use.</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Transaction notification config; Suspicious alert rules; Code generation mechanism; Code expiry config</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
-      <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr"/>
-      <c r="M40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>PD-29</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>WORKLOAD</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Mobile Device Security</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>App distribution and fake app monitoring</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>1. Verify publishing access controls.
 2. Confirm monitoring for fake/fraudulent apps.
@@ -4515,36 +5178,47 @@
 4. Review fake app incident history.</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>Publishing access controls; Fake app monitoring service; Takedown process docs; Fake app incident log</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr"/>
-      <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr"/>
-      <c r="L41" s="8" t="inlineStr"/>
-      <c r="M41" s="8" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="A5:M5"/>
+  <mergeCells count="22">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A34:M34"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A2:M2"/>
     <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A21:M21"/>
     <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A33:M33"/>
+    <mergeCell ref="A47:M47"/>
+    <mergeCell ref="A42:M42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4574,271 +5248,271 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Responsible</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Consolidate all test results — compile conclusions from all assessment sheets</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Assign risk ratings (High/Medium/Low) to each finding based on likelihood and impact</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>R-03</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Map findings to specific regulatory references (Appendix clauses, Part D items)</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>R-04</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Draft recommendations with specific remediation steps, responsible parties, and timelines</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Distinguish must-fix-before-go-live findings from post-launch improvements (for pre-impl)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Conduct quality assurance / peer review of working papers and findings</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Conduct findings walkthrough with FI management</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>R-08</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Incorporate management responses and agreed action plans</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>R-09</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Form Part C attestation opinion: Type A (Clean), Type B (With Exceptions), or Type C (Adverse)</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Prepare the formal report in Appendix 7 Part A format</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>R-11</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Confirm independence declaration and Part C compliance statement</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>R-12</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Obtain FI management sign-off on report and management action plans</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>R-13</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Prepare executive summary for designated board committee (per 8.3)</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>R-14</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Attend board committee meeting to present findings (if required)</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>R-15</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Document board committee directives and incorporate into final report</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>R-16</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Issue final signed report</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr"/>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4880,156 +5554,156 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Assessment Criteria</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Evidence / Justification</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Compliant?</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Independence</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>The IESP is independent of the FI's technology operations and the systems/services being assessed. No conflicts of interest exist between the IESP and the FI.</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Competence</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>The IESP team has relevant professional qualifications (CISA, CISSP, CCSP, CSP-specific certs), certifications, and experience in the subject matter being assessed.</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>The assessment covers ALL areas specified in the relevant appendix (Appendix 10, Appendix 9, or Part D as applicable). No required areas were excluded without documented justification.</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>The IESP uses a systematic, risk-based assessment methodology with clear criteria for evaluating controls. The methodology is documented and consistently applied.</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Findings are reported in the Appendix 7 Part A format with clear risk ratings and actionable recommendations. The report is complete, accurate, and traceable to evidence.</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Quality Assurance</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Internal QA processes were followed, including peer review of assessment work by a qualified reviewer who did not perform the assessment.</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">

--- a/audit-work-programs/IESP-DCRA-WorkProgram.xlsx
+++ b/audit-work-programs/IESP-DCRA-WorkProgram.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Methodology &amp; Approach" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scoping" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Planning" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DCRA Assessment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Appendix 7 Part D" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Reporting &amp; Attestation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Part C Self-Assessment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology &amp; Approach" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planning" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCRA Assessment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix 7 Part D" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporting &amp; Attestation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part C Self-Assessment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring Dashboard" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -70,7 +73,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +90,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,6 +159,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5764,4 +5797,426 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SCORING DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total Compliant</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <f>SUM(B19:B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Total Partially Compliant</t>
+        </is>
+      </c>
+      <c r="B6" s="16">
+        <f>SUM(C19:C20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total Non-Compliant</t>
+        </is>
+      </c>
+      <c r="B7" s="17">
+        <f>SUM(D19:D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Total N/A</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>SUM(E19:E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Total Not Assessed</t>
+        </is>
+      </c>
+      <c r="B9" s="9">
+        <f>SUM(F19:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Total Test Steps</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>SUM(G19:G20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Overall Compliance %</t>
+        </is>
+      </c>
+      <c r="B11" s="19">
+        <f>IF((B10-B8-B9)=0,"—",B5/(B10-B8-B9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PART C OPINION INDICATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Opinion Type</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <f>IF(B7&gt;5,"Type C (Adverse)",IF(B7&gt;0,"Type B (With Exceptions)",IF(B6&lt;=3,"Type A (Clean)","Type B (With Exceptions)")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Criteria:</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Type A (Clean): NC=0 and PC&lt;=3  |  Type B (With Exceptions): NC&gt;0 and NC&lt;=5  |  Type C (Adverse): NC&gt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>PER-SHEET BREAKDOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Partially Compliant</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Not Assessed</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Total Steps</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Compliance %</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>DCRA Assessment</t>
+        </is>
+      </c>
+      <c r="B19" s="15">
+        <f>COUNTIF('DCRA Assessment'!L:L,"Compliant")</f>
+        <v/>
+      </c>
+      <c r="C19" s="16">
+        <f>COUNTIF('DCRA Assessment'!L:L,"Partially Compliant")</f>
+        <v/>
+      </c>
+      <c r="D19" s="17">
+        <f>COUNTIF('DCRA Assessment'!L:L,"Non-Compliant")</f>
+        <v/>
+      </c>
+      <c r="E19" s="18">
+        <f>COUNTIF('DCRA Assessment'!L:L,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F19" s="9">
+        <f>COUNTIFS('DCRA Assessment'!A:A,"&lt;&gt;",'DCRA Assessment'!L:L,"=")-COUNTIF('DCRA Assessment'!A:A,"Ref")</f>
+        <v/>
+      </c>
+      <c r="G19" s="9">
+        <f>COUNTA('DCRA Assessment'!A:A)-COUNTIF('DCRA Assessment'!A:A,"Ref")-COUNTBLANK('DCRA Assessment'!A1)</f>
+        <v/>
+      </c>
+      <c r="H19" s="19">
+        <f>IF((G19-E19-F19)=0,"—",B19/(G19-E19-F19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Appendix 7 Part D</t>
+        </is>
+      </c>
+      <c r="B20" s="15">
+        <f>COUNTIF('Appendix 7 Part D'!L:L,"Compliant")</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>COUNTIF('Appendix 7 Part D'!L:L,"Partially Compliant")</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>COUNTIF('Appendix 7 Part D'!L:L,"Non-Compliant")</f>
+        <v/>
+      </c>
+      <c r="E20" s="18">
+        <f>COUNTIF('Appendix 7 Part D'!L:L,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>COUNTIFS('Appendix 7 Part D'!A:A,"&lt;&gt;",'Appendix 7 Part D'!L:L,"=")-COUNTIF('Appendix 7 Part D'!A:A,"Ref")</f>
+        <v/>
+      </c>
+      <c r="G20" s="9">
+        <f>COUNTA('Appendix 7 Part D'!A:A)-COUNTIF('Appendix 7 Part D'!A:A,"Ref")-COUNTBLANK('Appendix 7 Part D'!A1)</f>
+        <v/>
+      </c>
+      <c r="H20" s="19">
+        <f>IF((G20-E20-F20)=0,"—",B20/(G20-E20-F20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LEVEL BREAKDOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Partially Compliant</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Not Assessed</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="B25" s="15">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"ORG",'DCRA Assessment'!L:L,"Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"ORG",'Appendix 7 Part D'!L:L,"Compliant")</f>
+        <v/>
+      </c>
+      <c r="C25" s="16">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"ORG",'DCRA Assessment'!L:L,"Partially Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"ORG",'Appendix 7 Part D'!L:L,"Partially Compliant")</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"ORG",'DCRA Assessment'!L:L,"Non-Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"ORG",'Appendix 7 Part D'!L:L,"Non-Compliant")</f>
+        <v/>
+      </c>
+      <c r="E25" s="18">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"ORG",'DCRA Assessment'!L:L,"N/A")+COUNTIFS('Appendix 7 Part D'!B:B,"ORG",'Appendix 7 Part D'!L:L,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F25" s="9">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"ORG",'DCRA Assessment'!L:L,"=")+COUNTIFS('Appendix 7 Part D'!B:B,"ORG",'Appendix 7 Part D'!L:L,"=")</f>
+        <v/>
+      </c>
+      <c r="G25" s="9">
+        <f>SUM(B25:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="B26" s="15">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"PLATFORM",'DCRA Assessment'!L:L,"Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"PLATFORM",'Appendix 7 Part D'!L:L,"Compliant")</f>
+        <v/>
+      </c>
+      <c r="C26" s="16">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"PLATFORM",'DCRA Assessment'!L:L,"Partially Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"PLATFORM",'Appendix 7 Part D'!L:L,"Partially Compliant")</f>
+        <v/>
+      </c>
+      <c r="D26" s="17">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"PLATFORM",'DCRA Assessment'!L:L,"Non-Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"PLATFORM",'Appendix 7 Part D'!L:L,"Non-Compliant")</f>
+        <v/>
+      </c>
+      <c r="E26" s="18">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"PLATFORM",'DCRA Assessment'!L:L,"N/A")+COUNTIFS('Appendix 7 Part D'!B:B,"PLATFORM",'Appendix 7 Part D'!L:L,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F26" s="9">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"PLATFORM",'DCRA Assessment'!L:L,"=")+COUNTIFS('Appendix 7 Part D'!B:B,"PLATFORM",'Appendix 7 Part D'!L:L,"=")</f>
+        <v/>
+      </c>
+      <c r="G26" s="9">
+        <f>SUM(B26:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>WORKLOAD</t>
+        </is>
+      </c>
+      <c r="B27" s="15">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"WORKLOAD",'DCRA Assessment'!L:L,"Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"WORKLOAD",'Appendix 7 Part D'!L:L,"Compliant")</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"WORKLOAD",'DCRA Assessment'!L:L,"Partially Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"WORKLOAD",'Appendix 7 Part D'!L:L,"Partially Compliant")</f>
+        <v/>
+      </c>
+      <c r="D27" s="17">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"WORKLOAD",'DCRA Assessment'!L:L,"Non-Compliant")+COUNTIFS('Appendix 7 Part D'!B:B,"WORKLOAD",'Appendix 7 Part D'!L:L,"Non-Compliant")</f>
+        <v/>
+      </c>
+      <c r="E27" s="18">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"WORKLOAD",'DCRA Assessment'!L:L,"N/A")+COUNTIFS('Appendix 7 Part D'!B:B,"WORKLOAD",'Appendix 7 Part D'!L:L,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F27" s="9">
+        <f>COUNTIFS('DCRA Assessment'!B:B,"WORKLOAD",'DCRA Assessment'!L:L,"=")+COUNTIFS('Appendix 7 Part D'!B:B,"WORKLOAD",'Appendix 7 Part D'!L:L,"=")</f>
+        <v/>
+      </c>
+      <c r="G27" s="9">
+        <f>SUM(B27:F27)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>